--- a/Data/testDataUK.xlsx
+++ b/Data/testDataUK.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BAF8DA-32EC-4CA4-A1AB-078922D7AD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="127">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -201,6 +187,15 @@
     <t>ProposedPayGroupFinal</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Enrico Denesik' Employee:{undefined}TimeoutError: locator.fill: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('label:has-text("Last Name")')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>519 Recruitment (Fozac Hosoti (9575064) (Inherited))</t>
   </si>
   <si>
@@ -208,6 +203,12 @@
   </si>
   <si>
     <t>Mr</t>
+  </si>
+  <si>
+    <t>Enrico</t>
+  </si>
+  <si>
+    <t>Denesik</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -402,60 +403,60 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color rgb="FF040C28"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color rgb="FF040C28"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <u/>
+      <color theme="10"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="10"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color rgb="FF4A4A4A"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color rgb="FF4A4A4A"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <family val="1"/>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -467,7 +468,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -484,7 +485,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -496,7 +497,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -516,27 +517,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -962,10 +951,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BH4"/>
-  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
@@ -1024,8 +1013,7 @@
     <col min="58" max="58" width="15.33203125" style="1" customWidth="1"/>
     <col min="59" max="59" width="12.6640625" style="1" customWidth="1"/>
     <col min="60" max="60" width="26.21875" style="1" customWidth="1"/>
-    <col min="61" max="61" width="8.88671875" style="1" customWidth="1"/>
-    <col min="62" max="16384" width="8.88671875" style="1"/>
+    <col min="61" max="16384" width="8.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1210,63 +1198,72 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:60" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="7"/>
+    <row r="2" ht="15" customHeight="1" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="D2" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+        <v>61</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="I2" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L2" s="13">
         <v>45597</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Q2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="T2" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="R2" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>62</v>
-      </c>
       <c r="U2" s="16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="V2" s="17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="X2" s="18">
         <f>L2</f>
@@ -1277,97 +1274,97 @@
         <v>45687</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AA2" s="19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AC2" s="20" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AD2" s="21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AE2" s="22">
         <v>519</v>
       </c>
       <c r="AF2" s="22" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AG2" s="23">
         <v>37.5</v>
       </c>
       <c r="AH2" s="24" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI2" s="21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AJ2" s="25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AK2" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AL2" s="12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AP2" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AQ2" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AR2" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AS2" s="27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AU2" s="28">
         <v>35591</v>
       </c>
       <c r="AV2" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AX2" s="28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AY2" s="28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AZ2" s="28" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BA2" s="28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="BB2" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="BC2" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BD2" s="26" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="BE2" s="12">
         <v>601613</v>
@@ -1376,68 +1373,68 @@
         <v>31926819</v>
       </c>
       <c r="BG2" s="26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="BH2" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:60" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="15" customHeight="1" spans="4:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D3" s="8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L3" s="13">
         <v>45597</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Q3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="T3" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" s="12" t="s">
-        <v>62</v>
-      </c>
       <c r="U3" s="16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="V3" s="17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="X3" s="18">
         <f>L3</f>
@@ -1448,19 +1445,19 @@
         <v>45687</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AA3" s="19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AC3" s="20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AE3" s="22">
         <v>519</v>
@@ -1472,73 +1469,73 @@
         <v>40</v>
       </c>
       <c r="AH3" s="24" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AJ3" s="25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AK3" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AL3" s="12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AP3" s="30">
         <v>50000</v>
       </c>
       <c r="AQ3" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AR3" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AS3" s="27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AU3" s="28">
         <v>35591</v>
       </c>
       <c r="AV3" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AX3" s="28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AY3" s="28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AZ3" s="28" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BA3" s="28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="BB3" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="BC3" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BD3" s="26" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="BE3" s="12">
         <v>601613</v>
@@ -1547,68 +1544,68 @@
         <v>31926819</v>
       </c>
       <c r="BG3" s="26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="BH3" s="12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:60" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="15" customHeight="1" spans="4:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D4" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="33" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L4" s="13">
         <v>45597</v>
       </c>
       <c r="M4" s="31" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="T4" s="33" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="U4" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="V4" s="35" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="W4" s="33" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="X4" s="18">
         <f>L4</f>
@@ -1619,19 +1616,19 @@
         <v>45687</v>
       </c>
       <c r="Z4" s="33" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AA4" s="33" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AB4" s="27" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AC4" s="27" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AD4" s="27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AE4" s="36">
         <v>457</v>
@@ -1643,73 +1640,73 @@
         <v>15</v>
       </c>
       <c r="AH4" s="38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI4" s="27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AJ4" s="39" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AK4" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AL4" s="40" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AM4" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AN4" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AO4" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AP4" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AR4" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AS4" s="27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AT4" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AU4" s="28">
         <v>38081</v>
       </c>
       <c r="AV4" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AW4" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AX4" s="28" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AY4" s="28" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AZ4" s="28">
         <v>45020</v>
       </c>
       <c r="BA4" s="41" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="BB4" s="42" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="BC4" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BD4" s="9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BE4" s="40">
         <v>200052</v>
@@ -1718,25 +1715,37 @@
         <v>75849856</v>
       </c>
       <c r="BG4" s="26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="BH4" s="12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG4 Z2:Z4 W2:W4 T2:T4 K2:K4" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z4">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="AH2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="V3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="AH3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="V4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="AH4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="AH2" r:id="rId2"/>
+    <hyperlink ref="V3" r:id="rId3"/>
+    <hyperlink ref="AH3" r:id="rId4"/>
+    <hyperlink ref="V4" r:id="rId5"/>
+    <hyperlink ref="AH4" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
